--- a/artfynd/A 41375-2024 artfynd.xlsx
+++ b/artfynd/A 41375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104657375</v>
+        <v>137516961</v>
       </c>
       <c r="B2" t="n">
-        <v>99120</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Lillviken-Jutis, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580431</v>
+        <v>577882</v>
       </c>
       <c r="R2" t="n">
-        <v>7370634</v>
+        <v>7370186</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,28 +769,28 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657375</t>
+          <t>https://artportalen.se/Sighting/137516961</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104657380</v>
+        <v>104657375</v>
       </c>
       <c r="B3" t="n">
         <v>99120</v>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578156</v>
+        <v>580431</v>
       </c>
       <c r="R3" t="n">
-        <v>7370859</v>
+        <v>7370634</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,16 +899,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657380</t>
+          <t>https://artportalen.se/Sighting/104657375</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104657373</v>
+        <v>104657380</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,26 +916,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580266</v>
+        <v>578156</v>
       </c>
       <c r="R4" t="n">
-        <v>7370706</v>
+        <v>7370859</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,16 +1014,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657373</t>
+          <t>https://artportalen.se/Sighting/104657380</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5995485</v>
+        <v>137516962</v>
       </c>
       <c r="B5" t="n">
-        <v>99121</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,33 +1031,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223614</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ringselet, korsning Silvervägen/väg mot Tjärnberg, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579965</v>
+        <v>577876</v>
       </c>
       <c r="R5" t="n">
-        <v>7370817</v>
+        <v>7370168</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-08-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-08-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,29 +1105,246 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>rikt vägdike</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137516962</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104657373</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580266</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7370706</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657373</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5995485</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ringselet, korsning Silvervägen/väg mot Tjärnberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7370817</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-08-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-08-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>rikt vägdike</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Charlotte Nordgren</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5995485</t>
         </is>
@@ -1136,6 +1356,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41375-2024 artfynd.xlsx
+++ b/artfynd/A 41375-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137516961</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137516962</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
